--- a/projekt/TollUtdij 2025.12/SimiczZalan_TesztDokumentacio.xlsx
+++ b/projekt/TollUtdij 2025.12/SimiczZalan_TesztDokumentacio.xlsx
@@ -5,23 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zalan\OneDrive\Asztali gép\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zalan\Dokumentumok\GitHub\13_S2_1_Vizsgaremek2\projekt\TollUtdij 2025.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A749B1AC-91E2-4323-90A9-AF378B18A7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449CB01D-B208-4811-9534-B0522AAFB308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{70D12CFA-6C56-45B5-81A0-8FA42F16DDE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70D12CFA-6C56-45B5-81A0-8FA42F16DDE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="TesztEset1" sheetId="1" r:id="rId1"/>
-    <sheet name="TesztEset2" sheetId="2" r:id="rId2"/>
-    <sheet name="TesztEset3" sheetId="3" r:id="rId3"/>
-    <sheet name="TesztEset4" sheetId="4" r:id="rId4"/>
-    <sheet name="TesztEset5" sheetId="5" r:id="rId5"/>
-    <sheet name="TesztEset6" sheetId="7" r:id="rId6"/>
-    <sheet name="TesztEset8" sheetId="8" r:id="rId7"/>
-    <sheet name="TesztEset9" sheetId="9" r:id="rId8"/>
-    <sheet name="TesztEset10" sheetId="10" r:id="rId9"/>
+    <sheet name="TesztEset10" sheetId="10" r:id="rId1"/>
+    <sheet name="TesztEset1" sheetId="1" r:id="rId2"/>
+    <sheet name="TesztEset2" sheetId="2" r:id="rId3"/>
+    <sheet name="TesztEset3" sheetId="3" r:id="rId4"/>
+    <sheet name="TesztEset4" sheetId="4" r:id="rId5"/>
+    <sheet name="TesztEset5" sheetId="5" r:id="rId6"/>
+    <sheet name="TesztEset6" sheetId="7" r:id="rId7"/>
+    <sheet name="TesztEset8" sheetId="8" r:id="rId8"/>
+    <sheet name="TesztEset9" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="77">
   <si>
     <t>Mező</t>
   </si>
@@ -74,87 +74,32 @@
     <t>Test Script Test - Tényleges eredmény (Actual Result):</t>
   </si>
   <si>
-    <t>The cart should not contain any items.</t>
-  </si>
-  <si>
     <t>draft</t>
   </si>
   <si>
-    <t>Check the optional operation of cart functions.</t>
-  </si>
-  <si>
     <t>Nagy Huba Kende</t>
   </si>
   <si>
-    <t>30 seconds</t>
-  </si>
-  <si>
-    <t>1.Open https://academybugs.com
-2.Click the Find Bugs link on the navigation bar
-3.Open a product
-4.Open the cart at the bottom of right side menu
-5.Clear the cart if there are any items</t>
-  </si>
-  <si>
     <t>Not necessary</t>
-  </si>
-  <si>
-    <t>The caption of the "Return to Store" button is written with even spacing between letters</t>
-  </si>
-  <si>
-    <t>There is too much space before the last letter in "Return to Store"</t>
-  </si>
-  <si>
-    <t>Number of shown results test</t>
-  </si>
-  <si>
-    <t>Cart test</t>
   </si>
   <si>
     <t>Open https://academybugs.com
 Click the Find Bugs link on the navigation bar</t>
   </si>
   <si>
-    <t>Make sure every function woks on the main page.</t>
-  </si>
-  <si>
     <t>High severity</t>
   </si>
   <si>
     <t>Low severity</t>
   </si>
   <si>
-    <t>Click on the buttons to show a certain number of results at the top left</t>
-  </si>
-  <si>
-    <t>The selected number of results is displayed according to the clicked buttons</t>
-  </si>
-  <si>
-    <t>The page freezes when clicking on the numbers of results</t>
-  </si>
-  <si>
     <t>1 minute</t>
   </si>
   <si>
-    <t>Item sorting</t>
-  </si>
-  <si>
-    <t>Sorting shows accurate information</t>
-  </si>
-  <si>
     <t>2 minutes</t>
   </si>
   <si>
     <t>Moderate severity</t>
-  </si>
-  <si>
-    <t>Click on every sorting option</t>
-  </si>
-  <si>
-    <t>Sorting options show accurate information</t>
-  </si>
-  <si>
-    <t>Best rating and Oldest options return the same data.</t>
   </si>
   <si>
     <t>Account login and registry page test</t>
@@ -289,6 +234,115 @@
   </si>
   <si>
     <t>Egyezik az elvárt eredménnyl.</t>
+  </si>
+  <si>
+    <t>Sikeres regisztráció</t>
+  </si>
+  <si>
+    <t>funkcionális teszt</t>
+  </si>
+  <si>
+    <t>Az alkalmazás fut és elérhető: http://127.0.0.1:8000
+A partner login oldal elérhető: http://127.0.0.1:8000/partner/login
+A „Regisztráljon partnerként” link működik és elérhető a login oldalon
+A tesztben használt e-mail cím még nincs regisztrálva az adatbázisban: zalansimicz@gmail.com</t>
+  </si>
+  <si>
+    <t>Annak ellenőrzése, hogy partnerként történő regisztráció során az űrlap helyes kitöltése után a rendszer sikeresen létrehozza a partner fiókot az e-mail cím megerősítése után, és a felhasználó továbbléphet a dashboardra.</t>
+  </si>
+  <si>
+    <t>2perc</t>
+  </si>
+  <si>
+    <t>Nyisd meg a Partner bejelentkezési oldalt:
+http://127.0.0.1:8000/partner/login
+Kattints a „Regisztráljon partnerként” linkre.
+Töltsd ki a regisztrációs űrlapot az alábbi adatokkal:
+Cég neve: Demo Kft.
+Adószám: 12345678-1-26
+Székhely / cím: 1234 Demo, Demo utca 1.
+Kapcsolattartó neve: Kiss Pista
+Email cím: simiczzalan2005@gmail.com
+Jelszó: 12345678
+Jelszó megerősítése: 12345678
+Kattints a „Regisztráció” gombra.
+Erősítse meg az e-mail címét</t>
+  </si>
+  <si>
+    <t>A regisztráció sikeres.
+A rendszer:
+létrehozza az új partner fiókot az adatbázisban a felhasznalok táblában, illetve a cégek táblában is a hozzá tartozó céget,
+és átirányítja a felhasználót a partner bejelentkezéshez vagy a partner felületre.
+A felhasználó nem kap validációs hibát az űrlapon.</t>
+  </si>
+  <si>
+    <t>Sikeres login</t>
+  </si>
+  <si>
+    <t>Az alkalmazás fut: http://127.0.0.1:8000
+A partner login oldal elérhető:
+http://127.0.0.1:8000/partner/login
+A megadott felhasználó már regisztrálva van az adatbázisban:
+Email: zalansimicz@gmail.com
+Jelszó: 12345678</t>
+  </si>
+  <si>
+    <t>Annak ellenőrzése, hogy a partner felhasználó helyes email és jelszó megadása esetén sikeresen be tud jelentkezni a rendszerbe.</t>
+  </si>
+  <si>
+    <t>1-2perc</t>
+  </si>
+  <si>
+    <t>Nyisd meg a partner login oldalt:
+http://127.0.0.1:8000/partner/login
+Írd be az Email cím mezőbe:
+zalansimicz@gmail.com
+Írd be a Jelszó mezőbe:
+12345678
+Kattints a „Bejelentkezés” gombra.</t>
+  </si>
+  <si>
+    <t>A rendszer elfogadja a bejelentkezési adatokat.
+A felhasználó sikeresen bejelentkezik.
+A rendszer:
+átirányítja a partner dashboard oldalra
+vagy
+Nem jelenik meg hibaüzenet.</t>
+  </si>
+  <si>
+    <t>Sikertelen login</t>
+  </si>
+  <si>
+    <t>validációs teszt</t>
+  </si>
+  <si>
+    <t>Az alkalmazás fut:
+http://127.0.0.1:8000
+A partner login oldal elérhető:
+http://127.0.0.1:8000/partner/login
+A megadott email cím nem létezik a rendszerben, vagy a jelszó hibás</t>
+  </si>
+  <si>
+    <t>Annak ellenőrzése, hogy hibás email cím vagy jelszó megadása esetén:
+a rendszer nem engedi be a felhasználót,
+megfelelő hibaüzenetet jelenít meg,
+a felhasználó a login oldalon marad.</t>
+  </si>
+  <si>
+    <t>Nyisd meg a partner login oldalt:
+http://127.0.0.1:8000/partner/login
+Írd be az Email mezőbe:
+zalansimiczhibas@gmail.com
+Írd be a Jelszó mezőbe:
+1234567
+Kattints a „Bejelentkezés” gombra.</t>
+  </si>
+  <si>
+    <t>A rendszer nem engedi be a felhasználót.
+A login oldalon marad.
+Megjelenik a hibaüzenet:
+„Hibás email cím vagy jelszó”
+Nem történik átirányítás dashboard oldalra.</t>
   </si>
 </sst>
 </file>
@@ -714,8 +768,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA1C781-0C80-4018-8B3B-141250E60562}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="203.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1E2F04-C7C7-4BF7-B8B7-53E9F10A00B2}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" customWidth="1"/>
@@ -731,91 +903,99 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>23</v>
+      <c r="B2" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>21</v>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -824,9 +1004,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222FCA68-CA5A-4081-8552-02095C57CF96}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -842,91 +1022,99 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
+      <c r="B2" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="172.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -934,9 +1122,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E88C2B-25E3-4285-BF71-6699AB88C669}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -952,91 +1140,99 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="203.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="172.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>38</v>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1044,7 +1240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64FF86E-B3F6-4566-82D1-1C892F185422}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1066,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1074,7 +1270,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1082,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1090,7 +1286,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1098,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1106,7 +1302,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1114,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -1122,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1130,7 +1326,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1138,7 +1334,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1146,7 +1342,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA05CFE-9640-4452-8F2B-C16CB83E558A}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1176,15 +1372,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1192,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1200,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1208,7 +1404,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1216,7 +1412,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1224,7 +1420,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1232,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="94.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1240,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1248,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1256,7 +1452,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1264,7 +1460,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +1468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB4F6D4-0FF5-4FE1-BD76-CEE9AFE98FEA}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1294,15 +1490,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1310,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1318,7 +1514,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1326,7 +1522,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1334,7 +1530,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1342,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1350,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -1358,7 +1554,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1366,7 +1562,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1374,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1382,7 +1578,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E94E95F-0233-4D83-B8DD-4AF115CB9958}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1412,15 +1608,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1428,7 +1624,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
@@ -1436,7 +1632,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1444,7 +1640,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1452,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1460,7 +1656,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1468,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1476,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1484,7 +1680,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1492,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1500,7 +1696,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E33CD-FB51-4702-A92A-A2C18035FC04}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1530,15 +1726,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1546,7 +1742,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
@@ -1554,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1562,7 +1758,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1570,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1578,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1586,7 +1782,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1594,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1602,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
@@ -1610,7 +1806,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1618,125 +1814,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA1C781-0C80-4018-8B3B-141250E60562}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="203.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/projekt/TollUtdij 2025.12/SimiczZalan_TesztDokumentacio.xlsx
+++ b/projekt/TollUtdij 2025.12/SimiczZalan_TesztDokumentacio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zalan\Dokumentumok\GitHub\13_S2_1_Vizsgaremek2\projekt\TollUtdij 2025.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449CB01D-B208-4811-9534-B0522AAFB308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F400C1-079E-4A71-AC75-6CED7FEDFFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70D12CFA-6C56-45B5-81A0-8FA42F16DDE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="19" xr2:uid="{70D12CFA-6C56-45B5-81A0-8FA42F16DDE9}"/>
   </bookViews>
   <sheets>
     <sheet name="TesztEset10" sheetId="10" r:id="rId1"/>
@@ -22,6 +22,17 @@
     <sheet name="TesztEset6" sheetId="7" r:id="rId7"/>
     <sheet name="TesztEset8" sheetId="8" r:id="rId8"/>
     <sheet name="TesztEset9" sheetId="9" r:id="rId9"/>
+    <sheet name="Munka1" sheetId="11" r:id="rId10"/>
+    <sheet name="Munka2" sheetId="12" r:id="rId11"/>
+    <sheet name="Munka3" sheetId="13" r:id="rId12"/>
+    <sheet name="Munka4" sheetId="14" r:id="rId13"/>
+    <sheet name="Munka5" sheetId="15" r:id="rId14"/>
+    <sheet name="Munka6" sheetId="16" r:id="rId15"/>
+    <sheet name="Munka7" sheetId="17" r:id="rId16"/>
+    <sheet name="Munka8" sheetId="18" r:id="rId17"/>
+    <sheet name="Munka9" sheetId="19" r:id="rId18"/>
+    <sheet name="Munka10" sheetId="20" r:id="rId19"/>
+    <sheet name="Munka11" sheetId="21" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="125">
   <si>
     <t>Mező</t>
   </si>
@@ -77,113 +88,7 @@
     <t>draft</t>
   </si>
   <si>
-    <t>Nagy Huba Kende</t>
-  </si>
-  <si>
-    <t>Not necessary</t>
-  </si>
-  <si>
-    <t>Open https://academybugs.com
-Click the Find Bugs link on the navigation bar</t>
-  </si>
-  <si>
-    <t>High severity</t>
-  </si>
-  <si>
-    <t>Low severity</t>
-  </si>
-  <si>
-    <t>1 minute</t>
-  </si>
-  <si>
-    <t>2 minutes</t>
-  </si>
-  <si>
-    <t>Moderate severity</t>
-  </si>
-  <si>
-    <t>Account login and registry page test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login page information </t>
-  </si>
-  <si>
-    <t>Open a product
-Scroll down to the bottom of the right side menu
-Click "Sign In" to open the sign in page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The text under the New User section is in English
-</t>
-  </si>
-  <si>
-    <t>The text under the New User section is in another language</t>
-  </si>
-  <si>
-    <t>Hiba típusa (IssueType)</t>
-  </si>
-  <si>
-    <t>Open a product
-Scroll to the bottom and find the sign in form in the right side menu
-Enter any login and password that are not registered and click "Sign In"</t>
-  </si>
-  <si>
-    <t>The caption of the Sign In button is misaligned vertically</t>
-  </si>
-  <si>
-    <t>The caption of the Sign In button is centered vertically</t>
-  </si>
-  <si>
     <t>Hiba típusa (Issue Type)</t>
-  </si>
-  <si>
-    <t>All login functions and texts show up and work properly</t>
-  </si>
-  <si>
-    <t>Open a product
-Scroll down to the bottom of the right side menu
-Click "Sign In" without filling the form to open the Sign In page</t>
-  </si>
-  <si>
-    <t>The title of the password field is aligned the same as the field above</t>
-  </si>
-  <si>
-    <t>The title of the password field is not aligned the same as the field above</t>
-  </si>
-  <si>
-    <t>Product page test</t>
-  </si>
-  <si>
-    <t>crash</t>
-  </si>
-  <si>
-    <t>visual</t>
-  </si>
-  <si>
-    <t>Product page is working properly</t>
-  </si>
-  <si>
-    <t>Open a product
-Change the currency in the right side menu</t>
-  </si>
-  <si>
-    <t>The currency is changed as expected</t>
-  </si>
-  <si>
-    <t>The page freezes when changing the currency</t>
-  </si>
-  <si>
-    <t>content</t>
-  </si>
-  <si>
-    <t>Open a product,              Scroll down to the description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The short description and description of the product are in English
-</t>
-  </si>
-  <si>
-    <t>The short description and description of the product are not in English</t>
   </si>
   <si>
     <t>Sikertelen regisztráció (hibaüzenet megjelenítés)</t>
@@ -310,9 +215,6 @@
 Nem jelenik meg hibaüzenet.</t>
   </si>
   <si>
-    <t>Sikertelen login</t>
-  </si>
-  <si>
     <t>validációs teszt</t>
   </si>
   <si>
@@ -329,20 +231,349 @@
 a felhasználó a login oldalon marad.</t>
   </si>
   <si>
+    <t>A rendszer nem engedi be a felhasználót.
+A login oldalon marad.
+Megjelenik a hibaüzenet:
+„Hibás email cím vagy jelszó”
+Nem történik átirányítás dashboard oldalra.</t>
+  </si>
+  <si>
+    <t>Sikertelen login (rossz jelszó)</t>
+  </si>
+  <si>
+    <t>Nyisd meg a partner login oldalt:
+http://127.0.0.1:8000/partner/login
+Írd be az Email mezőbe:
+zalansimicz@gmail.com
+Írd be a Jelszó mezőbe:
+1234567
+Kattints a „Bejelentkezés” gombra.</t>
+  </si>
+  <si>
+    <t>Sikertelen login (rossz email)</t>
+  </si>
+  <si>
     <t>Nyisd meg a partner login oldalt:
 http://127.0.0.1:8000/partner/login
 Írd be az Email mezőbe:
 zalansimiczhibas@gmail.com
 Írd be a Jelszó mezőbe:
-1234567
+12345678
 Kattints a „Bejelentkezés” gombra.</t>
   </si>
   <si>
-    <t>A rendszer nem engedi be a felhasználót.
-A login oldalon marad.
-Megjelenik a hibaüzenet:
-„Hibás email cím vagy jelszó”
-Nem történik átirányítás dashboard oldalra.</t>
+    <t>Alkalmazott hozzáadása (sikeres)</t>
+  </si>
+  <si>
+    <t>funkcionális teszt (pozitív)</t>
+  </si>
+  <si>
+    <t>A partner login oldal elérhető
+Létező partner fiók
+A megadott email cím még nem szerepel a rendszerben</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a rendszer sikeresen létrehozza az új alkalmazottat érvényes adatok megadása esetén.</t>
+  </si>
+  <si>
+    <t>3perc</t>
+  </si>
+  <si>
+    <t>Nyisd meg a partner login oldalt:
+http://127.0.0.1:8000/partner/login
+Add meg az email címet: zalansimicz@gmail.com
+Add meg a jelszót: 12345678
+Kattints a „Bejelentkezés” gombra
+Kattints az „Alkalmazottak” menüpontra
+Töltsd ki a mezőket:
+Név: Teszt Alkalmazott
+Email: tesztalkalmazott3@gmail.com
+Jelszó: 12345678
+Jelszó megerősítés: 12345678
+Kattints az „Alkalmazott létrehozása” gombra</t>
+  </si>
+  <si>
+    <t>Megjelenik az üzenet:
+„Az új felhasználó sikeresen hozzáadásra került.”
+Az alkalmazott megjelenik a listában.</t>
+  </si>
+  <si>
+    <t>Alkalmazott hozzáadása (sikertelen)</t>
+  </si>
+  <si>
+    <t>funkcionális teszt (negatív)</t>
+  </si>
+  <si>
+    <t>A rendszer fut
+A megadott email cím már szerepel az alkalmazottak között</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a rendszer nem engedi duplikált email cím használatát.</t>
+  </si>
+  <si>
+    <t>Jelentkezz be partner fiókkal
+Navigálj az „Alkalmazottak” menüpontra
+Add meg a már létező email címet
+Kattints az „Alkalmazott létrehozása” gombra</t>
+  </si>
+  <si>
+    <t>Az alkalmazott nem jön létre
+Hibaüzenet jelenik meg
+Az alkalmazott lista nem változik</t>
+  </si>
+  <si>
+    <t>Alkalmazott inaktiválása</t>
+  </si>
+  <si>
+    <t>Az adott alkalmazott létezik
+Státusza: Aktív</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy az alkalmazott státusza Inaktívra változtatható.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+Alkalmazottak menüpont megnyitása
+A megfelelő sorban kattintás a „Letiltás” gombra</t>
+  </si>
+  <si>
+    <t>A státusz „Inaktív”-ra változik.</t>
+  </si>
+  <si>
+    <t>Alkalmazott aktiválása</t>
+  </si>
+  <si>
+    <t>Az alkalmazott létezik
+Státusza: Inaktív</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy az alkalmazott újra aktiválható.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+Alkalmazottak menüpont megnyitása
+„Aktiválás” gomb megnyomása</t>
+  </si>
+  <si>
+    <t>A státusz „Aktív”-ra változik.</t>
+  </si>
+  <si>
+    <t>Útdíj kalkulátor menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Funkcionális teszt (navigáció)</t>
+  </si>
+  <si>
+    <t>A partner login oldal elérhető
+Érvényes partner felhasználó létezik</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a „Útdíj Kalkulátor” menüpont sikeresen megnyitható bejelentkezés után.</t>
+  </si>
+  <si>
+    <t>Nyisd meg a login oldalt
+Add meg a helyes email címet
+Add meg a helyes jelszót
+Kattints a „Bejelentkezés” gombra
+Kattints az „Útdíj Kalkulátor” menüpontra</t>
+  </si>
+  <si>
+    <t>Az Útdíj Kalkulátor oldal betöltődik
+Az oldal címe vagy tartalma megjelenik</t>
+  </si>
+  <si>
+    <t>Alkalmazottak menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Sikeres bejelentkezés</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy az „Alkalmazottak” oldal elérhető a menüből.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+„Alkalmazottak” menüpont kiválasztása</t>
+  </si>
+  <si>
+    <t>Az Alkalmazottak oldal megjelenik.</t>
+  </si>
+  <si>
+    <t>Sofőrök menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a „Sofőrök” oldal elérhető.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+„Sofőrök” menüpont kiválasztása</t>
+  </si>
+  <si>
+    <t>Az Sofőrök oldal megjelenik.</t>
+  </si>
+  <si>
+    <t>Flotta menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a „Flotta” oldal elérhető.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+„Flotta” menüpont kiválasztása</t>
+  </si>
+  <si>
+    <t>Az Flotta oldal megjelenik.</t>
+  </si>
+  <si>
+    <t>Riportok menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a „Riportok” oldal elérhető.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+„Riportok” menüpont kiválasztása</t>
+  </si>
+  <si>
+    <t>Az Riportok oldal megjelenik.</t>
+  </si>
+  <si>
+    <t>Beállítások menüpont megnyitása</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a „Beállítások” oldal elérhető.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés
+„Beállítások” menüpont kiválasztása</t>
+  </si>
+  <si>
+    <t>Az Beállítások oldal megjelenik.</t>
+  </si>
+  <si>
+    <t>Új sofőr hozzáadás</t>
+  </si>
+  <si>
+    <t>functional test (CRUD – create)</t>
+  </si>
+  <si>
+    <t>A partner portál elérhető: http://127.0.0.1:8000/partner/login
+Létezik érvényes partner felhasználó: zalansimicz@gmail.com / 12345678
+A „Sofőrök” menüpont elérhető bejelentkezés után
+A rendszer engedi új sofőr rögzítését</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy új sofőr sikeresen létrehozható, és a mentés után megjelenik a listában.</t>
+  </si>
+  <si>
+    <t>Nyisd meg a bejelentkezési oldalt.
+Add meg az email címet: zalansimicz@gmail.com
+Add meg a jelszót: 12345678
+Kattints a „Bejelentkezés” gombra.
+Kattints a „Sofőrök” menüpontra.
+Kattints az „Új sofőr” gombra.
+Várd meg, amíg a driverForm megjelenik.
+Állítsd az „Aktív” mezőt „Igen”-re.
+Töltsd ki a szöveges mezőket:
+Név: Teszt Elek1
+Személyi azonosító: 224195ME
+Telefonszám: +36300803236
+Cím: 6760 Kistelek, Tisza utca 11.
+Adószám: 12345678-1-26
+Állítsd be a születési dátumot: 2000-01-01
+Kattints a „Mentés” gombra.
+Ellenőrizd, hogy a listában megjelenik: Teszt Elek1</t>
+  </si>
+  <si>
+    <t>A „Mentés” után a sofőr rögzítésre kerül.
+A sofőrlista tartalmazza a Teszt Elek1 nevet.</t>
+  </si>
+  <si>
+    <t>Sofőr inaktiválása</t>
+  </si>
+  <si>
+    <t>functional test (CRUD – update státusz)</t>
+  </si>
+  <si>
+    <t>partner felhasználó be tud jelentkezni
+A sofőrlista tartalmaz egy sort: Jani Király
+A sorban elérhető a „Státusz váltása” gomb</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a sofőr státusza „Inaktív”-ra váltható.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés a partner portálra.
+Navigálás a „Sofőrök” menüpontra.
+A Jani Király sorában kattints a „Státusz váltása” gombra.
+Ellenőrizd, hogy megjelenik az „Inaktív” státusz.</t>
+  </si>
+  <si>
+    <t>A kiválasztott sofőr státusza „Inaktív”-ra változik.</t>
+  </si>
+  <si>
+    <t>Sofőr aktiválása</t>
+  </si>
+  <si>
+    <t>A Jani Király sofőr létezik
+A sofőr éppen „Inaktív” (különben a váltás nem biztos, hogy „Aktív”-ra megy)</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a sofőr státusza „Aktív”-ra váltható.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés.
+„Sofőrök” menü megnyitása.
+Jani Király sorában „Státusz váltása” gomb megnyomása.
+Ellenőrizd, hogy megjelenik az „Aktív” státusz.</t>
+  </si>
+  <si>
+    <t>A sofőr státusza „Aktív”-ra változik.</t>
+  </si>
+  <si>
+    <t>Sofőr név módosítása</t>
+  </si>
+  <si>
+    <t>functional test (CRUD – update)</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a sofőr neve módosítható és mentés után megjelenik a listában.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés.
+„Sofőrök” menü megnyitása.
+Jani Király sorában kattints a „Szerkesztés” gombra.
+A név mezőt írd át: Jani Nem Kiraly
+Kattints a „Mentés” gombra.
+Ellenőrizd, hogy a listában megjelenik: Jani Nem Kiraly</t>
+  </si>
+  <si>
+    <t>A sofőr neve sikeresen frissül.
+A listában az új név látható.</t>
+  </si>
+  <si>
+    <t>Sofőr törlése</t>
+  </si>
+  <si>
+    <t>functional test (CRUD – delete)</t>
+  </si>
+  <si>
+    <t>Létezik sofőr: Jani a Boss Apja
+A sorban elérhető a „Törlés” gomb
+Törléskor megerősítő alert jelenik meg</t>
+  </si>
+  <si>
+    <t>Ellenőrizni, hogy a sofőr törölhető, és a megerősítés után eltűnik a listából.</t>
+  </si>
+  <si>
+    <t>Bejelentkezés.
+„Sofőrök” menü megnyitása.
+Jani a Boss Apja sorában kattints a „Törlés” gombra.
+Az alert ablakban kattints az „OK” gombra (ACCEPT).
+Ellenőrizd, hogy a lista már nem tartalmazza: Jani a Boss Apja</t>
+  </si>
+  <si>
+    <t>A törlés megerősítése után a sofőr törlődik.
+A sofőr neve nem szerepel többé a listában.</t>
   </si>
 </sst>
 </file>
@@ -435,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -451,9 +682,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -789,15 +1017,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -813,7 +1041,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -821,7 +1049,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -829,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -837,7 +1065,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -845,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -853,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -861,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -869,7 +1097,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -877,7 +1105,1187 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185C69DE-3E34-4BE7-A12D-ED93FF1D1392}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD36E35D-9520-43E6-98D8-67C45FDDEDD3}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80728C24-568B-4BDD-864B-BFB9545DE03E}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F620B124-2F79-406D-A4D5-236D4FF97EEF}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB98D7A2-394E-4A49-80C3-7D4EEEB6F71C}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78268038-6A08-44FC-B1C9-31AEE371E3CF}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE9C875-063A-4637-9F98-B3A509D8A2E1}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="219" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2420A243-83B2-41C0-B87D-0D810DADE725}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.21875" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="172.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBDF3BD-881F-41A4-A666-509195F8CA24}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92332EE-77C7-4FE3-8718-FFAB2025A903}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="281.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -907,15 +2315,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -931,7 +2339,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -939,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -947,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -955,7 +2363,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="92.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -963,7 +2371,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -971,7 +2379,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -979,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -987,7 +2395,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -995,12 +2403,130 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3F68DC-0926-42BB-B8B6-DBC19A27F16F}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1026,15 +2552,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1050,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
@@ -1058,7 +2584,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1066,7 +2592,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1074,7 +2600,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1082,7 +2608,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="156.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1090,7 +2616,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1098,7 +2624,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1106,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1114,7 +2640,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1144,15 +2670,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1168,7 +2694,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1176,7 +2702,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1184,7 +2710,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1192,7 +2718,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1200,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="203.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1208,7 +2734,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1216,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="172.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1224,7 +2750,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1232,7 +2758,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1242,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64FF86E-B3F6-4566-82D1-1C892F185422}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.109375" customWidth="1"/>
@@ -1257,92 +2783,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
+      <c r="B2" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:2" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:2" ht="172.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1368,19 +2902,19 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
+      <c r="B2" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1391,20 +2925,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="94.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1412,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1420,7 +2954,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1428,15 +2962,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="94.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="406.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1444,15 +2978,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="94.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1460,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1490,15 +3024,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1509,12 +3043,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1522,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1530,7 +3064,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1538,7 +3072,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1546,15 +3080,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="125.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1562,15 +3096,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1578,7 +3112,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1608,15 +3142,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1627,20 +3161,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1648,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1656,7 +3190,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1664,15 +3198,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1680,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1688,7 +3222,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1696,7 +3230,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1726,15 +3260,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1745,12 +3279,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1758,7 +3292,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1766,7 +3300,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1774,7 +3308,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1782,15 +3316,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1798,15 +3332,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1814,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
